--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -34,6 +34,7 @@
     <definedName function="false" hidden="false" name="DSCR_Q4_2023" vbProcedure="false">Q4_2023!$D$14</definedName>
     <definedName function="false" hidden="false" name="DSCR_Q4_2024" vbProcedure="false">Q4_2024!$D$14</definedName>
     <definedName function="false" hidden="false" name="DSCR_Q4_2025" vbProcedure="false">Q4_2025!$D$14</definedName>
+    <definedName function="false" hidden="false" name="Ledger_DemoToday" vbProcedure="false">_meta!$B$4</definedName>
     <definedName function="false" hidden="false" name="Outstanding_Q1_2024" vbProcedure="false">Q1_2024!$D$12</definedName>
     <definedName function="false" hidden="false" name="Outstanding_Q1_2025" vbProcedure="false">Q1_2025!$D$12</definedName>
     <definedName function="false" hidden="false" name="Outstanding_Q1_2026" vbProcedure="false">Q1_2026!$D$12</definedName>
@@ -166,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T08:51:04+00:00</t>
+    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -258,16 +259,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -291,253 +288,253 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <f aca="false">Q4_2023!D14</f>
         <v>1.42</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="0" t="n">
         <f aca="false">Q4_2023!D10</f>
         <v>1.25</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="0" t="str">
         <f aca="false">Q4_2023!D15</f>
         <v>pass</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="0" t="n">
         <f aca="false">Q4_2023!D12</f>
         <v>50400000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <f aca="false">Q1_2024!D14</f>
         <v>1.38</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="0" t="n">
         <f aca="false">Q1_2024!D10</f>
         <v>1.25</v>
       </c>
-      <c r="D3" s="1" t="str">
+      <c r="D3" s="0" t="str">
         <f aca="false">Q1_2024!D15</f>
         <v>pass</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="0" t="n">
         <f aca="false">Q1_2024!D12</f>
         <v>49400000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="0" t="n">
         <f aca="false">Q2_2024!D14</f>
         <v>1.31</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="0" t="n">
         <f aca="false">Q2_2024!D10</f>
         <v>1.25</v>
       </c>
-      <c r="D4" s="1" t="str">
+      <c r="D4" s="0" t="str">
         <f aca="false">Q2_2024!D15</f>
         <v>pass</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="0" t="n">
         <f aca="false">Q2_2024!D12</f>
         <v>49400000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <f aca="false">Q3_2024!D14</f>
         <v>1.27</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="0" t="n">
         <f aca="false">Q3_2024!D10</f>
         <v>1.25</v>
       </c>
-      <c r="D5" s="1" t="str">
+      <c r="D5" s="0" t="str">
         <f aca="false">Q3_2024!D15</f>
         <v>pass</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <f aca="false">Q3_2024!D12</f>
         <v>48300000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <f aca="false">Q4_2024!D14</f>
         <v>1.24</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="0" t="n">
         <f aca="false">Q4_2024!D10</f>
         <v>1.25</v>
       </c>
-      <c r="D6" s="1" t="str">
+      <c r="D6" s="0" t="str">
         <f aca="false">Q4_2024!D15</f>
         <v>fail</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <f aca="false">Q4_2024!D12</f>
         <v>48300000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <f aca="false">Q1_2025!D14</f>
         <v>1.23</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="0" t="n">
         <f aca="false">Q1_2025!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D7" s="1" t="str">
+      <c r="D7" s="0" t="str">
         <f aca="false">Q1_2025!D15</f>
         <v>pass</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <f aca="false">Q1_2025!D12</f>
         <v>47000000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <f aca="false">Q2_2025!D14</f>
         <v>1.29</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="0" t="n">
         <f aca="false">Q2_2025!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D8" s="1" t="str">
+      <c r="D8" s="0" t="str">
         <f aca="false">Q2_2025!D15</f>
         <v>pass</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <f aca="false">Q2_2025!D12</f>
         <v>47000000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <f aca="false">Q3_2025!D14</f>
         <v>1.33</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="0" t="n">
         <f aca="false">Q3_2025!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D9" s="1" t="str">
+      <c r="D9" s="0" t="str">
         <f aca="false">Q3_2025!D15</f>
         <v>pass</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <f aca="false">Q3_2025!D12</f>
         <v>45600000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="0" t="n">
         <f aca="false">Q4_2025!D14</f>
         <v>1.36</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="0" t="n">
         <f aca="false">Q4_2025!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D10" s="1" t="str">
+      <c r="D10" s="0" t="str">
         <f aca="false">Q4_2025!D15</f>
         <v>pass</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <f aca="false">Q4_2025!D12</f>
         <v>45600000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="0" t="n">
         <f aca="false">Q1_2026!D14</f>
         <v>1.34</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="0" t="n">
         <f aca="false">Q1_2026!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D11" s="1" t="str">
+      <c r="D11" s="0" t="str">
         <f aca="false">Q1_2026!D15</f>
         <v>pass</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <f aca="false">Q1_2026!D12</f>
         <v>44100000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="0" t="n">
         <f aca="false">Q2_2026!D14</f>
         <v>1.37</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="0" t="n">
         <f aca="false">Q2_2026!D10</f>
         <v>1.2</v>
       </c>
-      <c r="D12" s="1" t="str">
+      <c r="D12" s="0" t="str">
         <f aca="false">Q2_2026!D15</f>
         <v>pass</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <f aca="false">Q2_2026!D12</f>
         <v>44100000</v>
       </c>
@@ -561,86 +558,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1854900</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1327750</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1363875</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>45600000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -664,86 +661,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1822300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1500000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1219800</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1359900</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>44100000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -767,86 +764,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1863100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1500000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1219800</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1359900</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>44100000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -871,31 +868,31 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>39</v>
       </c>
     </row>
@@ -918,86 +915,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1225600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1726200</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>863100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>50400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1021,86 +1018,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1863700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1701000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1350500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>49400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1124,86 +1121,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1769200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1701000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1350500</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>49400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1227,86 +1224,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1757200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1100000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1667250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1383625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>48300000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1330,86 +1327,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1715700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1100000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1667250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1383625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>48300000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>fail</v>
       </c>
@@ -1433,86 +1430,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1638700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1300000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1364475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1332237.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>47000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1536,86 +1533,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1718600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1300000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1364475</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1332237.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>47000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>
@@ -1639,86 +1636,86 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="0" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1814000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="0" t="n">
         <v>1400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="0" t="n">
         <v>1327750</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
         <v>1363875</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="0" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="0" t="n">
         <v>45600000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="0" t="n">
         <f aca="false">ROUND(D5/D8,2)</f>
         <v>1.33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="0" t="str">
         <f aca="false">IF(D14&gt;=D10,"pass","fail")</f>
         <v>pass</v>
       </c>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Result</t>
   </si>
   <si>
-    <t xml:space="preserve">Outstanding after half (EUR)</t>
+    <t xml:space="preserve">Outstanding after half (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">Q4_2023</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">Period</t>
   </si>
   <si>
-    <t xml:space="preserve">CFADS (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal, half-year (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interest, half-year (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt service, quarter (EUR) = (principal + interest) / 2</t>
+    <t xml:space="preserve">CFADS (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal, half-year (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest, half-year (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt service, quarter (USD) = (principal + interest) / 2</t>
   </si>
   <si>
     <t xml:space="preserve">Covenant threshold (min DSCR)</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T19:07:43+00:00</t>
+    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -326,7 +326,7 @@
       </c>
       <c r="E2" s="0" t="n">
         <f aca="false">Q4_2023!D12</f>
-        <v>50400000</v>
+        <v>13220400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -347,7 +347,7 @@
       </c>
       <c r="E3" s="0" t="n">
         <f aca="false">Q1_2024!D12</f>
-        <v>49400000</v>
+        <v>12979200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -368,7 +368,7 @@
       </c>
       <c r="E4" s="0" t="n">
         <f aca="false">Q2_2024!D12</f>
-        <v>49400000</v>
+        <v>12979200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -389,7 +389,7 @@
       </c>
       <c r="E5" s="0" t="n">
         <f aca="false">Q3_2024!D12</f>
-        <v>48300000</v>
+        <v>12703700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -410,7 +410,7 @@
       </c>
       <c r="E6" s="0" t="n">
         <f aca="false">Q4_2024!D12</f>
-        <v>48300000</v>
+        <v>12703700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,7 +431,7 @@
       </c>
       <c r="E7" s="0" t="n">
         <f aca="false">Q1_2025!D12</f>
-        <v>47000000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -452,7 +452,7 @@
       </c>
       <c r="E8" s="0" t="n">
         <f aca="false">Q2_2025!D12</f>
-        <v>47000000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -473,7 +473,7 @@
       </c>
       <c r="E9" s="0" t="n">
         <f aca="false">Q3_2025!D12</f>
-        <v>45600000</v>
+        <v>12050000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -494,7 +494,7 @@
       </c>
       <c r="E10" s="0" t="n">
         <f aca="false">Q4_2025!D12</f>
-        <v>45600000</v>
+        <v>12050000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -515,7 +515,7 @@
       </c>
       <c r="E11" s="0" t="n">
         <f aca="false">Q1_2026!D12</f>
-        <v>44100000</v>
+        <v>11671800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -536,7 +536,7 @@
       </c>
       <c r="E12" s="0" t="n">
         <f aca="false">Q2_2026!D12</f>
-        <v>44100000</v>
+        <v>11671800</v>
       </c>
     </row>
   </sheetData>
@@ -580,7 +580,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1854900</v>
+        <v>537300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -588,7 +588,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1400000</v>
+        <v>344000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -596,7 +596,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1327750</v>
+        <v>446184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -605,7 +605,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1363875</v>
+        <v>395092</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -621,7 +621,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>45600000</v>
+        <v>12050000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -683,7 +683,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1822300</v>
+        <v>515800</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -691,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1500000</v>
+        <v>378200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -699,7 +699,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1219800</v>
+        <v>391625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -708,7 +708,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1359900</v>
+        <v>384912.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -724,7 +724,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>44100000</v>
+        <v>11671800</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -786,7 +786,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1863100</v>
+        <v>527300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -794,7 +794,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1500000</v>
+        <v>378200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -802,7 +802,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1219800</v>
+        <v>391625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -811,7 +811,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1359900</v>
+        <v>384912.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -827,7 +827,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>44100000</v>
+        <v>11671800</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -937,7 +937,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1225600</v>
+        <v>513900</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -945,7 +945,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0</v>
+        <v>206900</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -953,7 +953,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1726200</v>
+        <v>516951.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -962,7 +962,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>863100</v>
+        <v>361925.525</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>50400000</v>
+        <v>13220400</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1040,7 +1040,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1863700</v>
+        <v>526800</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1000000</v>
+        <v>241200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1701000</v>
+        <v>522205.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1350500</v>
+        <v>381702.9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,7 +1081,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>49400000</v>
+        <v>12979200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,7 +1143,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1769200</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1151,7 +1151,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1000000</v>
+        <v>241200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1159,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1701000</v>
+        <v>522205.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1350500</v>
+        <v>381702.9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1184,7 +1184,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>49400000</v>
+        <v>12979200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1246,7 +1246,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1757200</v>
+        <v>500500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1254,7 +1254,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1100000</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1262,7 +1262,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1667250</v>
+        <v>512678.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1383625</v>
+        <v>394089.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1287,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>48300000</v>
+        <v>12703700</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1349,7 +1349,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1715700</v>
+        <v>488700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1357,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1100000</v>
+        <v>275500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1365,7 +1365,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1667250</v>
+        <v>512678.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1383625</v>
+        <v>394089.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1390,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>48300000</v>
+        <v>12703700</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1452,7 +1452,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1638700</v>
+        <v>471700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1460,7 +1460,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1300000</v>
+        <v>309700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1468,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1364475</v>
+        <v>457333.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1332237.5</v>
+        <v>383516.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1493,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>47000000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1555,7 +1555,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1718600</v>
+        <v>494700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1563,7 +1563,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1300000</v>
+        <v>309700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1571,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1364475</v>
+        <v>457333.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1332237.5</v>
+        <v>383516.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1596,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>47000000</v>
+        <v>12394000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1658,7 +1658,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1814000</v>
+        <v>525500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1400000</v>
+        <v>344000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1327750</v>
+        <v>446184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D8" s="0" t="n">
         <f aca="false">(D6+D7)/2</f>
-        <v>1363875</v>
+        <v>395092</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>45600000</v>
+        <v>12050000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T22:07:38+00:00</t>
+    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">demo_today</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15</t>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
 </sst>
 </file>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T10:25:41+00:00</t>
+    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T16:24:22+00:00</t>
+    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T18:49:07+00:00</t>
+    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T19:37:43+00:00</t>
+    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10T20:12:49+00:00</t>
+    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T07:14:19+00:00</t>
+    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>

--- a/seed_data/excel/Covenant_Report.xlsx
+++ b/seed_data/excel/Covenant_Report.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
+    <t xml:space="preserve">2026-10-12T13:12:20+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
